--- a/analysis_output/潜在層アンケート分析.xlsx
+++ b/analysis_output/潜在層アンケート分析.xlsx
@@ -9,22 +9,28 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="説明・注意点" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参加意向_全体" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="潜在層_年代構成" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="潜在層_企画" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="潜在層_情報源" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企画_年代別" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報源_年代別" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考_3つ以内の企画" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="潜在層_職業構成" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企画_学生比較" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報源_学生比較" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="潜在層_年代構成" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="潜在層_企画" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="潜在層_情報源" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企画_年代別" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報源_年代別" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考_3つ以内の企画" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'説明・注意点'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'説明・注意点'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'参加意向_全体'!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'潜在層_年代構成'!$A$1:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'潜在層_企画'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'潜在層_情報源'!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'企画_年代別'!$A$1:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'情報源_年代別'!$A$1:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'参考_3つ以内の企画'!$A$1:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'潜在層_職業構成'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'企画_学生比較'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'情報源_学生比較'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'潜在層_年代構成'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'潜在層_企画'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'潜在層_情報源'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'企画_年代別'!$A$1:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'情報源_年代別'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'参考_3つ以内の企画'!$A$1:$D$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -492,7 +498,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>（作業用2）アンバサダー2026-10-16時点データ.xlsx のコピー.xlsx のコピー.xlsx - シート2.csv</t>
+          <t>（作業用2.2）アンバサダー2026-10-16時点データ.xlsx のコピー.xlsx のコピー.xlsx - シート2.csv</t>
         </is>
       </c>
     </row>
@@ -540,7 +546,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>20代以下は少数のため若者の傾向の断定は避ける。学生区分はなく、年代から学生とは判断しない。</t>
+          <t>20代以下は少数のため若者の傾向の断定は避ける。職業欄（Occupation）の「学生」で判別できる。年代と学生区分は別に集計する。</t>
         </is>
       </c>
     </row>
@@ -592,8 +598,577 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>学生区分</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Occupationが学生の回答は全体9人、潜在層4人。学生・非学生比較は少数回答の参考値。非学生と大人世代は同義ではない。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
+  <autoFilter ref="A1:B12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="75" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>10代（n=2）選択率%</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>20代（n=8）選択率%</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>30代（n=46）選択率%</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>40代（n=67）選択率%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>50代（n=175）選択率%</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>60代（n=132）選択率%</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>70代（n=37）選択率%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>80代以上（n=5）選択率%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>InstagramやXなどのSNS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>テレビや雑誌などSNS以外のメディア</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>学校や職場、お店に設置されているチラシ・ポスター</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>家族や友人からの情報</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>本アカウントやニュースメディアなどのLINE公式アカウントからの通知</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>自治体の広報誌やホームページ</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>関連情報を一切入手しない</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="75" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>選択人数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>選択率（%）</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>分母（人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>参加特典（ノベルティ、ポイントなど）がもらえる</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>短時間（10〜15分程度）でサクッと体験できる</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>美味しい飲食ブースがある</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1人でも楽しめる</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>スタンプラリーや謎解きなどのゲーム企画がある</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>自分の行動が環境にどのようにつながるか分かる</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>体験型企画（ワークショップや工作など）がある</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ステージイベント（ショーやトークなど）がある</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>企業の取り組みについて学べる</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SNSなどで発信・共有したくなる企画である</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>友人やサークル仲間と一緒に楽しめる</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>自分自身が企画や運営に参加できる</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>クイズ形式で対戦ができる</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>学生生活の中で実践できる内容である</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -693,6 +1268,618 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="75" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>構成比（%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>会社員・団体職員</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>パート・アルバイト</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>専業主婦・専業主夫</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>無職</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="75" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学生人数（n=4）</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>学生選択率%</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>非学生人数（n=468）</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>非学生選択率%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1人でも楽しめる</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>34.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SNSなどで発信・共有したくなる企画である</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>クイズ形式で対戦ができる</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>スタンプラリーや謎解きなどのゲーム企画がある</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ステージイベント（ショーやトークなど）がある</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>企業の取り組みについて学べる</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>体験型企画（ワークショップや工作など）がある</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>参加特典（ノベルティ、ポイントなど）がもらえる</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>友人やサークル仲間と一緒に楽しめる</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>学生生活の中で実践できる内容である</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>短時間（10〜15分程度）でサクッと体験できる</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>美味しい飲食ブースがある</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>自分の行動が環境にどのようにつながるか分かる</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>自分自身が企画や運営に参加できる</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="75" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学生人数（n=4）</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>学生選択率%</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>非学生人数（n=468）</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>非学生選択率%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>InstagramやXなどのSNS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>テレビや雑誌などSNS以外のメディア</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>学校や職場、お店に設置されているチラシ・ポスター</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>家族や友人からの情報</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>本アカウントやニュースメディアなどのLINE公式アカウントからの通知</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>自治体の広報誌やホームページ</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>関連情報を一切入手しない</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,7 +2015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1047,7 +2234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1175,7 +2362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1680,561 +2867,4 @@
   <autoFilter ref="A1:I15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="75" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>10代（n=2）選択率%</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>20代（n=8）選択率%</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>30代（n=46）選択率%</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>40代（n=67）選択率%</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>50代（n=175）選択率%</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>60代（n=132）選択率%</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>70代（n=37）選択率%</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>80代以上（n=5）選択率%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>InstagramやXなどのSNS</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>テレビや雑誌などSNS以外のメディア</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>学校や職場、お店に設置されているチラシ・ポスター</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>家族や友人からの情報</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>本アカウントやニュースメディアなどのLINE公式アカウントからの通知</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>自治体の広報誌やホームページ</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>関連情報を一切入手しない</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="75" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>選択人数</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>選択率（%）</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>分母（人）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>参加特典（ノベルティ、ポイントなど）がもらえる</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>193</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>短時間（10〜15分程度）でサクッと体験できる</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>美味しい飲食ブースがある</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>1人でも楽しめる</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>スタンプラリーや謎解きなどのゲーム企画がある</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>自分の行動が環境にどのようにつながるか分かる</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>体験型企画（ワークショップや工作など）がある</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>ステージイベント（ショーやトークなど）がある</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>企業の取り組みについて学べる</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SNSなどで発信・共有したくなる企画である</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>友人やサークル仲間と一緒に楽しめる</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>自分自身が企画や運営に参加できる</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>クイズ形式で対戦ができる</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>学生生活の中で実践できる内容である</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>360</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D15"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>